--- a/doc_templates/tpl_devreq.xlsx
+++ b/doc_templates/tpl_devreq.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\2026년_프로젝트\P02.서비스\[2026.01.01]KICPA운영및개발\01.계약문서\2026_0320_[한공회]2026년03월분_콘텐츠개발계약(신규14)_조세지원본부\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\P08.AI\04.한공회콘텐츠관리Tool\01.자료\정산자료 템플릿\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72AC06C-0A23-4DE4-AC69-C29249BE3594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A182F24-54C8-4B5D-B7D9-B95150BE959A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="콘텐츠개발내역" sheetId="1" r:id="rId1"/>
     <sheet name="단가" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="품의" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>단가</t>
   </si>
@@ -151,10 +151,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>* 조세지원본부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>* 사무직원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,10 +159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>신규</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1~4시간</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,27 +191,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">이철재 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>03월 콘텐츠 개발 내역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>법인세 실무1(2026)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>법인세 실무2(2026)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>법인세 실무3(2026)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>양도소득세 실무(2026)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -471,7 +443,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -514,9 +486,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -570,9 +539,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -896,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -915,13 +881,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
+      <c r="A1" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="1"/>
@@ -930,269 +896,154 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" ht="27" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="N1" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8"/>
+    </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>40</v>
-      </c>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="21">
-        <v>3</v>
-      </c>
-      <c r="G4" s="22">
-        <v>3</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="16"/>
-      <c r="L4" s="7">
-        <v>500000</v>
-      </c>
-      <c r="M4" s="7">
-        <f t="shared" ref="M4" si="0">L4*F4</f>
-        <v>1500000</v>
-      </c>
-      <c r="N4" s="8">
-        <f t="shared" ref="N4" si="1">M4*1.1</f>
-        <v>1650000.0000000002</v>
-      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>40</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="13"/>
-      <c r="F5" s="21">
-        <v>3</v>
-      </c>
-      <c r="G5" s="22">
-        <v>3</v>
-      </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="7">
-        <v>500000</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" ref="M5:M7" si="2">L5*F5</f>
-        <v>1500000</v>
-      </c>
-      <c r="N5" s="8">
-        <f t="shared" ref="N5:N7" si="3">M5*1.1</f>
-        <v>1650000.0000000002</v>
-      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>40</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="21">
-        <v>4</v>
-      </c>
-      <c r="G6" s="22">
-        <v>4</v>
-      </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="16"/>
-      <c r="L6" s="7">
-        <v>500000</v>
-      </c>
-      <c r="M6" s="7">
-        <f t="shared" si="2"/>
-        <v>2000000</v>
-      </c>
-      <c r="N6" s="8">
-        <f t="shared" si="3"/>
-        <v>2200000</v>
-      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="8"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="21">
-        <v>4</v>
-      </c>
-      <c r="G7" s="22">
-        <v>4</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="7">
-        <v>500000</v>
-      </c>
-      <c r="M7" s="7">
-        <f t="shared" si="2"/>
-        <v>2000000</v>
-      </c>
-      <c r="N7" s="8">
-        <f t="shared" si="3"/>
-        <v>2200000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
+      <c r="A7" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="18">
-        <f>SUM(F4:F7)</f>
-        <v>14</v>
-      </c>
-      <c r="G8" s="18">
-        <f>SUM(G4:G7)</f>
-        <v>14</v>
-      </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="18">
-        <f>SUM(K4:K7)</f>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="17">
+        <f>SUM(F3:F6)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="19">
-        <f>SUM(M4:M7)</f>
-        <v>7000000</v>
-      </c>
-      <c r="N8" s="19">
-        <f>SUM(N4:N7)</f>
-        <v>7700000</v>
+      <c r="G7" s="17">
+        <f>SUM(G3:G6)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="17">
+        <f>SUM(K3:K6)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="18">
+        <f>SUM(M3:M6)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="18">
+        <f>SUM(N3:N6)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A8:E8"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:E7"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1211,74 +1062,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="36"/>
+      <c r="C1" s="34"/>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>500000</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="26">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="26">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C6" s="26">
         <v>500000</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="27">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="27">
-        <v>500000</v>
-      </c>
-    </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="36"/>
+      <c r="C8" s="34"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>50000</v>
       </c>
     </row>
@@ -1286,43 +1137,43 @@
       <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>160000</v>
       </c>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="36"/>
+      <c r="B13" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="34"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="27">
+      <c r="B15" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="26">
         <v>100000</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>33</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1358,7 +1209,7 @@
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -1391,130 +1242,74 @@
       <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="21">
-        <v>3</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="7">
-        <v>500000</v>
-      </c>
-      <c r="H5" s="7">
-        <v>1500000</v>
-      </c>
-      <c r="I5" s="8">
-        <v>1650000.0000000002</v>
-      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="21">
-        <v>3</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="7">
-        <v>500000</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1500000</v>
-      </c>
-      <c r="I6" s="8">
-        <v>1650000.0000000002</v>
-      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="21">
-        <v>4</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="7">
-        <v>500000</v>
-      </c>
-      <c r="H7" s="7">
-        <v>2000000</v>
-      </c>
-      <c r="I7" s="8">
-        <v>2200000</v>
-      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="21">
-        <v>4</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="7">
-        <v>500000</v>
-      </c>
-      <c r="H8" s="7">
-        <v>2000000</v>
-      </c>
-      <c r="I8" s="8">
-        <v>2200000</v>
-      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="24">
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="23">
         <f>SUM(E5:E8)</f>
-        <v>14</v>
-      </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
       <c r="H9" s="11">
         <f>SUM(H5:H8)</f>
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="11">
         <f>SUM(I5:I8)</f>
-        <v>7700000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -1548,25 +1343,25 @@
         <v>1</v>
       </c>
       <c r="C13" s="6"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="21"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="6"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="32">
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="31">
         <f>SUM(E13:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="11">
         <f>SUM(H13:H13)</f>
         <v>0</v>

--- a/doc_templates/tpl_devreq.xlsx
+++ b/doc_templates/tpl_devreq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\P08.AI\04.한공회콘텐츠관리Tool\01.자료\정산자료 템플릿\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A182F24-54C8-4B5D-B7D9-B95150BE959A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F4E7DD-46B8-4CFA-A389-E5275A404DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>단가</t>
   </si>
@@ -148,10 +148,6 @@
   </si>
   <si>
     <t>크로마키</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 사무직원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -443,7 +439,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -535,9 +531,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -881,13 +874,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
+      <c r="A1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="1"/>
@@ -897,7 +890,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="27" x14ac:dyDescent="0.3">
@@ -1009,13 +1002,13 @@
       <c r="N6" s="8"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="17">
         <f>SUM(F3:F6)</f>
         <v>0</v>
@@ -1062,10 +1055,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="24" t="s">
@@ -1085,7 +1078,7 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="26">
         <v>500000</v>
@@ -1093,7 +1086,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="26">
         <v>500000</v>
@@ -1101,7 +1094,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="26">
         <v>500000</v>
@@ -1112,10 +1105,10 @@
       <c r="C7" s="29"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="34"/>
+      <c r="C8" s="33"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="24" t="s">
@@ -1147,14 +1140,14 @@
       <c r="C12" s="27"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="34"/>
+      <c r="B13" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="33"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>18</v>
@@ -1162,7 +1155,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="26">
         <v>100000</v>
@@ -1170,10 +1163,10 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B3:I14"/>
+  <dimension ref="B3:I9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -1209,7 +1202,7 @@
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -1287,11 +1280,11 @@
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="23">
         <f>SUM(E5:E8)</f>
         <v>0</v>
@@ -1307,74 +1300,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="31">
-        <f>SUM(E13:E13)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="11">
-        <f>SUM(H13:H13)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="11">
-        <f>SUM(I13:I13)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B14:D14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc_templates/tpl_devreq.xlsx
+++ b/doc_templates/tpl_devreq.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>단가(vat별도)/시간</t>
+          <t>단가(vat별도)/일</t>
         </is>
       </c>
     </row>
